--- a/test/sales.xlsx
+++ b/test/sales.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abhiraj Das\Documents\DMSBackend\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6154DEBF-90BA-4339-9368-9E71A428E569}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6034321-4D6C-412C-AF33-2C9C233ED160}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,11 +16,12 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="177">
   <si>
     <t>branch</t>
   </si>
@@ -127,12 +128,6 @@
     <t>gst_rate2</t>
   </si>
   <si>
-    <t>Bangalore Branch</t>
-  </si>
-  <si>
-    <t>Kolkata Branch</t>
-  </si>
-  <si>
     <t>Connaught Place</t>
   </si>
   <si>
@@ -145,12 +140,6 @@
     <t>Salt Lake</t>
   </si>
   <si>
-    <t>Shivajinagar</t>
-  </si>
-  <si>
-    <t>9876543210</t>
-  </si>
-  <si>
     <t>8765432109</t>
   </si>
   <si>
@@ -286,27 +275,6 @@
     <t>GST789012</t>
   </si>
   <si>
-    <t>PAN1234567</t>
-  </si>
-  <si>
-    <t>PAN2345678</t>
-  </si>
-  <si>
-    <t>PAN3456789</t>
-  </si>
-  <si>
-    <t>PAN4567890</t>
-  </si>
-  <si>
-    <t>PAN5678901</t>
-  </si>
-  <si>
-    <t>PAN6789012</t>
-  </si>
-  <si>
-    <t>PAN7890123</t>
-  </si>
-  <si>
     <t>456 Avenue, Town</t>
   </si>
   <si>
@@ -352,9 +320,6 @@
     <t>Monitor</t>
   </si>
   <si>
-    <t>SSD</t>
-  </si>
-  <si>
     <t>Tablet</t>
   </si>
   <si>
@@ -427,9 +392,6 @@
     <t>B2B</t>
   </si>
   <si>
-    <t>B2C</t>
-  </si>
-  <si>
     <t>TDS</t>
   </si>
   <si>
@@ -442,15 +404,6 @@
     <t>Keyboard</t>
   </si>
   <si>
-    <t>LAN Cable</t>
-  </si>
-  <si>
-    <t>RAM</t>
-  </si>
-  <si>
-    <t>Charger</t>
-  </si>
-  <si>
     <t>Wireless Mouse</t>
   </si>
   <si>
@@ -520,18 +473,9 @@
     <t>mumbai</t>
   </si>
   <si>
-    <t>Branch B</t>
-  </si>
-  <si>
     <t>Santosh Nagar</t>
   </si>
   <si>
-    <t>Branch C</t>
-  </si>
-  <si>
-    <t>Branch D</t>
-  </si>
-  <si>
     <t>c:/Users/Abhiraj Das/Documents/book66.xlsx</t>
   </si>
   <si>
@@ -556,13 +500,58 @@
     <t>GST001313131</t>
   </si>
   <si>
-    <t>MALAD WEST</t>
-  </si>
-  <si>
-    <t>Board</t>
-  </si>
-  <si>
-    <t>DUSTBIN</t>
+    <t>PANAS4567S</t>
+  </si>
+  <si>
+    <t>PANSD4678W</t>
+  </si>
+  <si>
+    <t>PANDF7412E</t>
+  </si>
+  <si>
+    <t>ASDFG7414F</t>
+  </si>
+  <si>
+    <t>ASDFG7415S</t>
+  </si>
+  <si>
+    <t>ASDFG7412A</t>
+  </si>
+  <si>
+    <t>ASDFG7418A</t>
+  </si>
+  <si>
+    <t>Dustbin</t>
+  </si>
+  <si>
+    <t>po_no</t>
+  </si>
+  <si>
+    <t>po_date</t>
+  </si>
+  <si>
+    <t>Branch A</t>
+  </si>
+  <si>
+    <t>Malad west</t>
+  </si>
+  <si>
+    <t>sdfghj</t>
+  </si>
+  <si>
+    <t>rtyuio</t>
+  </si>
+  <si>
+    <t>Door</t>
+  </si>
+  <si>
+    <t>lkjhgf</t>
+  </si>
+  <si>
+    <t>nbvx</t>
+  </si>
+  <si>
+    <t>B2C-L</t>
   </si>
 </sst>
 </file>
@@ -594,7 +583,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -617,16 +606,30 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -931,15 +934,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AJ8"/>
+  <dimension ref="A1:AL8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -986,7 +991,7 @@
         <v>14</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>15</v>
@@ -1048,55 +1053,61 @@
       <c r="AJ1" s="1" t="s">
         <v>34</v>
       </c>
+      <c r="AK1" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="AL1" s="3" t="s">
+        <v>168</v>
+      </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>165</v>
+        <v>149</v>
       </c>
       <c r="B2" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="C2">
-        <v>11111111111</v>
+        <v>7418529630</v>
       </c>
       <c r="D2" t="s">
-        <v>173</v>
+        <v>154</v>
       </c>
       <c r="E2" t="s">
-        <v>174</v>
+        <v>155</v>
       </c>
       <c r="F2" t="s">
-        <v>175</v>
+        <v>156</v>
       </c>
       <c r="G2" t="s">
-        <v>176</v>
+        <v>157</v>
       </c>
       <c r="H2" s="2">
         <v>43961</v>
       </c>
       <c r="I2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="J2" s="2">
         <v>37387</v>
       </c>
       <c r="K2" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="L2" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="M2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="N2" t="s">
-        <v>177</v>
+        <v>158</v>
       </c>
       <c r="O2" t="s">
-        <v>88</v>
+        <v>159</v>
       </c>
       <c r="P2" t="s">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="Q2">
         <v>1</v>
@@ -1108,105 +1119,111 @@
         <v>0</v>
       </c>
       <c r="T2" t="s">
+        <v>90</v>
+      </c>
+      <c r="U2">
+        <v>9876543210</v>
+      </c>
+      <c r="V2" t="s">
+        <v>98</v>
+      </c>
+      <c r="W2" t="s">
         <v>101</v>
       </c>
-      <c r="U2" t="s">
-        <v>42</v>
-      </c>
-      <c r="V2" t="s">
-        <v>179</v>
-      </c>
-      <c r="W2" t="s">
-        <v>113</v>
-      </c>
       <c r="X2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="Y2">
         <v>1200</v>
       </c>
       <c r="Z2" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="AA2">
         <v>18</v>
       </c>
       <c r="AB2" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="AC2" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="AD2">
         <v>6</v>
       </c>
       <c r="AE2" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="AF2" t="s">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="AG2" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="AH2">
         <v>1500</v>
       </c>
       <c r="AI2" t="s">
-        <v>157</v>
+        <v>141</v>
       </c>
       <c r="AJ2">
         <v>18</v>
       </c>
+      <c r="AK2">
+        <v>112</v>
+      </c>
+      <c r="AL2" s="2">
+        <v>45629</v>
+      </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>165</v>
+        <v>149</v>
       </c>
       <c r="B3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C3" t="s">
-        <v>43</v>
+        <v>35</v>
+      </c>
+      <c r="C3">
+        <v>8765432109</v>
       </c>
       <c r="D3" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="G3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="H3" s="2">
         <v>44752</v>
       </c>
       <c r="I3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="J3" s="2">
         <v>37388</v>
       </c>
       <c r="K3" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="L3" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="M3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="N3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="O3" t="s">
-        <v>89</v>
+        <v>160</v>
       </c>
       <c r="P3" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="Q3">
         <v>1</v>
@@ -1218,105 +1235,111 @@
         <v>1</v>
       </c>
       <c r="T3" t="s">
+        <v>91</v>
+      </c>
+      <c r="U3" t="s">
+        <v>39</v>
+      </c>
+      <c r="V3" t="s">
+        <v>97</v>
+      </c>
+      <c r="W3" t="s">
         <v>102</v>
       </c>
-      <c r="U3" t="s">
-        <v>43</v>
-      </c>
-      <c r="V3" t="s">
-        <v>108</v>
-      </c>
-      <c r="W3" t="s">
-        <v>114</v>
-      </c>
       <c r="X3" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="Y3">
         <v>1234</v>
       </c>
       <c r="Z3" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="AA3">
         <v>18</v>
       </c>
       <c r="AB3" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="AC3" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="AD3">
         <v>5</v>
       </c>
       <c r="AE3" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="AF3" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="AG3" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="AH3">
         <v>800</v>
       </c>
       <c r="AI3" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="AJ3">
         <v>18</v>
       </c>
+      <c r="AK3">
+        <v>1213</v>
+      </c>
+      <c r="AL3" s="2">
+        <v>45630</v>
+      </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>169</v>
       </c>
       <c r="B4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E4" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G4" t="s">
         <v>63</v>
-      </c>
-      <c r="G4" t="s">
-        <v>67</v>
       </c>
       <c r="H4" s="2">
         <v>45117</v>
       </c>
       <c r="I4" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="J4" s="2">
         <v>37420</v>
       </c>
       <c r="K4" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="L4" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="M4" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="N4" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="O4" t="s">
-        <v>90</v>
+        <v>161</v>
       </c>
       <c r="P4" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="Q4">
         <v>1</v>
@@ -1328,105 +1351,111 @@
         <v>0</v>
       </c>
       <c r="T4" t="s">
+        <v>92</v>
+      </c>
+      <c r="U4" t="s">
+        <v>40</v>
+      </c>
+      <c r="V4" t="s">
+        <v>98</v>
+      </c>
+      <c r="W4" t="s">
         <v>103</v>
       </c>
-      <c r="U4" t="s">
-        <v>44</v>
-      </c>
-      <c r="V4" t="s">
-        <v>109</v>
-      </c>
-      <c r="W4" t="s">
-        <v>115</v>
-      </c>
       <c r="X4" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="Y4">
         <v>1300</v>
       </c>
       <c r="Z4" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="AA4">
         <v>18</v>
       </c>
       <c r="AB4" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="AC4" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="AD4">
         <v>8</v>
       </c>
       <c r="AE4" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="AF4" t="s">
-        <v>145</v>
+        <v>129</v>
       </c>
       <c r="AG4" t="s">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="AH4">
         <v>1000</v>
       </c>
       <c r="AI4" t="s">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="AJ4">
         <v>18</v>
       </c>
+      <c r="AK4">
+        <v>123</v>
+      </c>
+      <c r="AL4" s="2">
+        <v>45631</v>
+      </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B5" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F5" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="G5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="H5" s="2">
         <v>44754</v>
       </c>
       <c r="I5" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="J5" s="2">
         <v>37360</v>
       </c>
       <c r="K5" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="L5" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="M5" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="N5" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="O5" t="s">
-        <v>91</v>
+        <v>162</v>
       </c>
       <c r="P5" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="Q5">
         <v>1</v>
@@ -1438,105 +1467,111 @@
         <v>1</v>
       </c>
       <c r="T5" t="s">
+        <v>93</v>
+      </c>
+      <c r="U5" t="s">
+        <v>41</v>
+      </c>
+      <c r="V5" t="s">
+        <v>126</v>
+      </c>
+      <c r="W5" t="s">
         <v>104</v>
       </c>
-      <c r="U5" t="s">
-        <v>45</v>
-      </c>
-      <c r="V5" t="s">
-        <v>139</v>
-      </c>
-      <c r="W5" t="s">
-        <v>116</v>
-      </c>
       <c r="X5" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="Y5">
         <v>2300</v>
       </c>
       <c r="Z5" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="AA5">
         <v>18</v>
       </c>
       <c r="AB5" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="AC5" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="AD5">
         <v>34</v>
       </c>
       <c r="AE5" t="s">
-        <v>140</v>
+        <v>166</v>
       </c>
       <c r="AF5" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="AG5" t="s">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="AH5">
         <v>1700</v>
       </c>
       <c r="AI5" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="AJ5">
         <v>18</v>
       </c>
+      <c r="AK5">
+        <v>1243</v>
+      </c>
+      <c r="AL5" s="2">
+        <v>45632</v>
+      </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D6" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E6" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F6" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G6" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="H6" s="2">
         <v>45466</v>
       </c>
       <c r="I6" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="J6" s="2">
         <v>44635</v>
       </c>
       <c r="K6" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="L6" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="M6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="N6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="O6" t="s">
-        <v>92</v>
+        <v>163</v>
       </c>
       <c r="P6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="Q6">
         <v>1</v>
@@ -1548,105 +1583,111 @@
         <v>0</v>
       </c>
       <c r="T6" t="s">
+        <v>94</v>
+      </c>
+      <c r="U6" t="s">
+        <v>42</v>
+      </c>
+      <c r="V6" t="s">
+        <v>174</v>
+      </c>
+      <c r="W6" t="s">
         <v>105</v>
       </c>
-      <c r="U6" t="s">
-        <v>46</v>
-      </c>
-      <c r="V6" t="s">
-        <v>110</v>
-      </c>
-      <c r="W6" t="s">
-        <v>117</v>
-      </c>
       <c r="X6" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="Y6">
         <v>300</v>
       </c>
       <c r="Z6" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="AA6">
         <v>18</v>
       </c>
       <c r="AB6" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="AC6" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="AD6">
         <v>8</v>
       </c>
       <c r="AE6" t="s">
-        <v>141</v>
+        <v>175</v>
       </c>
       <c r="AF6" t="s">
-        <v>147</v>
+        <v>131</v>
       </c>
       <c r="AG6" t="s">
-        <v>154</v>
+        <v>138</v>
       </c>
       <c r="AH6">
         <v>1600</v>
       </c>
       <c r="AI6" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="AJ6">
         <v>18</v>
       </c>
+      <c r="AK6">
+        <v>1212</v>
+      </c>
+      <c r="AL6" s="2">
+        <v>45633</v>
+      </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>36</v>
+        <v>169</v>
       </c>
       <c r="B7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D7" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E7" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F7" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="G7" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="H7" s="2">
         <v>44756</v>
       </c>
       <c r="I7" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="J7" s="2">
         <v>37392</v>
       </c>
       <c r="K7" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="L7" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="M7" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="N7" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="O7" t="s">
-        <v>93</v>
+        <v>164</v>
       </c>
       <c r="P7" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="Q7">
         <v>1</v>
@@ -1658,105 +1699,111 @@
         <v>1</v>
       </c>
       <c r="T7" t="s">
+        <v>95</v>
+      </c>
+      <c r="U7" t="s">
+        <v>43</v>
+      </c>
+      <c r="V7" t="s">
+        <v>99</v>
+      </c>
+      <c r="W7" t="s">
         <v>106</v>
       </c>
-      <c r="U7" t="s">
-        <v>47</v>
-      </c>
-      <c r="V7" t="s">
-        <v>111</v>
-      </c>
-      <c r="W7" t="s">
-        <v>118</v>
-      </c>
       <c r="X7" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="Y7">
         <v>500</v>
       </c>
       <c r="Z7" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="AA7">
         <v>18</v>
       </c>
       <c r="AB7" t="s">
-        <v>135</v>
+        <v>176</v>
       </c>
       <c r="AC7" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="AD7">
         <v>18</v>
       </c>
       <c r="AE7" t="s">
-        <v>142</v>
+        <v>171</v>
       </c>
       <c r="AF7" t="s">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="AG7" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="AH7">
         <v>2400</v>
       </c>
       <c r="AI7" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="AJ7">
         <v>18</v>
       </c>
+      <c r="AK7">
+        <v>12343</v>
+      </c>
+      <c r="AL7" s="2">
+        <v>45634</v>
+      </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>169</v>
       </c>
       <c r="B8" t="s">
-        <v>41</v>
+        <v>150</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E8" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F8" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="G8" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="H8" s="2">
         <v>44757</v>
       </c>
       <c r="I8" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="J8" s="2">
         <v>45521</v>
       </c>
       <c r="K8" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="L8" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="M8" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="N8" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="O8" t="s">
-        <v>94</v>
+        <v>165</v>
       </c>
       <c r="P8" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="Q8">
         <v>1</v>
@@ -1768,55 +1815,61 @@
         <v>0</v>
       </c>
       <c r="T8" t="s">
+        <v>96</v>
+      </c>
+      <c r="U8" t="s">
+        <v>44</v>
+      </c>
+      <c r="V8" t="s">
+        <v>100</v>
+      </c>
+      <c r="W8" t="s">
         <v>107</v>
       </c>
-      <c r="U8" t="s">
-        <v>48</v>
-      </c>
-      <c r="V8" t="s">
-        <v>112</v>
-      </c>
-      <c r="W8" t="s">
-        <v>119</v>
-      </c>
       <c r="X8" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="Y8">
         <v>700</v>
       </c>
       <c r="Z8" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="AA8">
         <v>18</v>
       </c>
       <c r="AB8" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="AC8" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="AD8">
         <v>9</v>
       </c>
       <c r="AE8" t="s">
-        <v>142</v>
+        <v>172</v>
       </c>
       <c r="AF8" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="AG8" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="AH8">
         <v>2500</v>
       </c>
       <c r="AI8" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="AJ8">
         <v>18</v>
+      </c>
+      <c r="AK8">
+        <v>12454</v>
+      </c>
+      <c r="AL8" s="2">
+        <v>45635</v>
       </c>
     </row>
   </sheetData>
